--- a/shroom_shop/canned.xlsx
+++ b/shroom_shop/canned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AnreX\projects\_shrooms\shroom_shop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D4B580-1C9F-47EC-9CDF-653C3F8306A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36FFF6F-CF45-4496-A032-73AB76FDEFBE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="244">
   <si>
     <t>Name</t>
   </si>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>https://basket-15.wbbasket.ru/vol2261/part226103/226103802/images/big/1.webp;https://basket-15.wbbasket.ru/vol2261/part226103/226103802/images/big/2.webp;https://basket-15.wbbasket.ru/vol2261/part226103/226103802/images/big/3.webp;https://basket-15.wbbasket.ru/vol2261/part226103/226103802/images/big/4.webp</t>
-  </si>
-  <si>
-    <t>опята лесные</t>
   </si>
   <si>
     <t>опята, соль, вода, специи, уксусная кислота</t>
@@ -1479,7 +1476,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1488,70 +1485,70 @@
         <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="Z1" s="1"/>
     </row>
@@ -2010,22 +2007,22 @@
     </row>
     <row r="8" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
         <v>71</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>72</v>
       </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -2058,7 +2055,7 @@
         <v>60</v>
       </c>
       <c r="Q8" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="R8" t="s">
         <v>35</v>
@@ -2087,22 +2084,22 @@
     </row>
     <row r="9" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s">
         <v>75</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
       </c>
       <c r="C9" t="s">
         <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
         <v>29</v>
@@ -2164,22 +2161,22 @@
     </row>
     <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
         <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
@@ -2212,7 +2209,7 @@
         <v>27</v>
       </c>
       <c r="Q10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R10" t="s">
         <v>35</v>
@@ -2241,22 +2238,22 @@
     </row>
     <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
         <v>83</v>
       </c>
-      <c r="B11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>85</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>
@@ -2318,22 +2315,22 @@
     </row>
     <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
         <v>90</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" t="s">
-        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
         <v>29</v>
@@ -2395,22 +2392,22 @@
     </row>
     <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
         <v>29</v>
@@ -2437,13 +2434,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="O13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R13" t="s">
         <v>35</v>
@@ -2472,22 +2469,22 @@
     </row>
     <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
         <v>102</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
         <v>103</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
         <v>29</v>
@@ -2520,7 +2517,7 @@
         <v>60</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R14" t="s">
         <v>35</v>
@@ -2549,22 +2546,22 @@
     </row>
     <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
         <v>106</v>
-      </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>107</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G15" t="s">
         <v>29</v>
@@ -2591,13 +2588,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="O15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R15" t="s">
         <v>35</v>
@@ -2626,22 +2623,22 @@
     </row>
     <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
         <v>112</v>
       </c>
-      <c r="B16" t="s">
-        <v>113</v>
-      </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G16" t="s">
         <v>29</v>
@@ -2668,13 +2665,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="O16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R16" t="s">
         <v>35</v>
@@ -2703,22 +2700,22 @@
     </row>
     <row r="17" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
         <v>115</v>
       </c>
-      <c r="B17" t="s">
-        <v>116</v>
-      </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G17" t="s">
         <v>29</v>
@@ -2751,7 +2748,7 @@
         <v>27</v>
       </c>
       <c r="Q17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R17" t="s">
         <v>35</v>
@@ -2780,22 +2777,22 @@
     </row>
     <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
         <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G18" t="s">
         <v>29</v>
@@ -2857,22 +2854,22 @@
     </row>
     <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
         <v>127</v>
       </c>
-      <c r="B19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" t="s">
-        <v>128</v>
-      </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
         <v>29</v>
@@ -2881,7 +2878,7 @@
         <v>24</v>
       </c>
       <c r="I19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J19" t="s">
         <v>25</v>
@@ -2896,7 +2893,7 @@
         <v>27</v>
       </c>
       <c r="Q19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R19" t="s">
         <v>35</v>
@@ -2925,22 +2922,22 @@
     </row>
     <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" t="s">
         <v>131</v>
-      </c>
-      <c r="C20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G20" t="s">
         <v>29</v>
@@ -2949,7 +2946,7 @@
         <v>24</v>
       </c>
       <c r="I20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J20" t="s">
         <v>25</v>
@@ -2973,7 +2970,7 @@
         <v>27</v>
       </c>
       <c r="Q20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R20" t="s">
         <v>35</v>
@@ -3002,22 +2999,22 @@
     </row>
     <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G21" t="s">
         <v>29</v>
@@ -3047,10 +3044,10 @@
         <v>56</v>
       </c>
       <c r="P21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R21" t="s">
         <v>35</v>
@@ -3079,22 +3076,22 @@
     </row>
     <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" t="s">
         <v>143</v>
       </c>
-      <c r="B22" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" t="s">
-        <v>144</v>
-      </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G22" t="s">
         <v>29</v>
@@ -3103,7 +3100,7 @@
         <v>24</v>
       </c>
       <c r="I22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J22" t="s">
         <v>25</v>
@@ -3124,10 +3121,10 @@
         <v>56</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R22" t="s">
         <v>35</v>
@@ -3156,22 +3153,22 @@
     </row>
     <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C23" t="s">
         <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G23" t="s">
         <v>29</v>
@@ -3201,7 +3198,7 @@
         <v>56</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q23" t="s">
         <v>55</v>
@@ -3233,16 +3230,16 @@
     </row>
     <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" t="s">
         <v>153</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" t="s">
         <v>154</v>
-      </c>
-      <c r="C24" t="s">
-        <v>156</v>
-      </c>
-      <c r="D24" t="s">
-        <v>155</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -3278,7 +3275,7 @@
         <v>56</v>
       </c>
       <c r="P24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q24" t="s">
         <v>23</v>
@@ -3310,22 +3307,22 @@
     </row>
     <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" t="s">
         <v>157</v>
-      </c>
-      <c r="D25" t="s">
-        <v>158</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G25" t="s">
         <v>29</v>
@@ -3358,7 +3355,7 @@
         <v>27</v>
       </c>
       <c r="Q25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R25" t="s">
         <v>35</v>
@@ -3387,31 +3384,31 @@
     </row>
     <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" t="s">
         <v>166</v>
       </c>
-      <c r="B26" t="s">
-        <v>163</v>
-      </c>
-      <c r="C26" t="s">
-        <v>167</v>
-      </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H26" t="s">
         <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J26" t="s">
         <v>25</v>
@@ -3429,13 +3426,13 @@
         <v>3</v>
       </c>
       <c r="O26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R26" t="s">
         <v>35</v>
@@ -3464,22 +3461,22 @@
     </row>
     <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" t="s">
         <v>170</v>
       </c>
-      <c r="B27" t="s">
-        <v>171</v>
-      </c>
       <c r="C27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G27" t="s">
         <v>29</v>
@@ -3512,7 +3509,7 @@
         <v>27</v>
       </c>
       <c r="Q27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R27" t="s">
         <v>35</v>
@@ -3541,22 +3538,22 @@
     </row>
     <row r="28" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" t="s">
         <v>172</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
         <v>176</v>
-      </c>
-      <c r="C28" t="s">
-        <v>173</v>
-      </c>
-      <c r="D28" t="s">
-        <v>177</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G28" t="s">
         <v>29</v>
@@ -3586,10 +3583,10 @@
         <v>56</v>
       </c>
       <c r="P28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R28" t="s">
         <v>35</v>
@@ -3618,22 +3615,22 @@
     </row>
     <row r="29" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>178</v>
+      </c>
+      <c r="B29" t="s">
         <v>179</v>
       </c>
-      <c r="B29" t="s">
-        <v>180</v>
-      </c>
       <c r="C29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G29" t="s">
         <v>29</v>
@@ -3663,10 +3660,10 @@
         <v>56</v>
       </c>
       <c r="P29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R29" t="s">
         <v>35</v>
@@ -3695,22 +3692,22 @@
     </row>
     <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" t="s">
+        <v>180</v>
+      </c>
+      <c r="C30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" t="s">
         <v>182</v>
-      </c>
-      <c r="B30" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" t="s">
-        <v>173</v>
-      </c>
-      <c r="D30" t="s">
-        <v>183</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G30" t="s">
         <v>29</v>
@@ -3740,10 +3737,10 @@
         <v>56</v>
       </c>
       <c r="P30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R30" t="s">
         <v>35</v>
@@ -3772,22 +3769,22 @@
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
+        <v>183</v>
+      </c>
+      <c r="C31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
         <v>184</v>
-      </c>
-      <c r="C31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31" t="s">
-        <v>185</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G31" t="s">
         <v>29</v>
@@ -3820,7 +3817,7 @@
         <v>60</v>
       </c>
       <c r="Q31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R31" t="s">
         <v>35</v>
@@ -3849,22 +3846,22 @@
     </row>
     <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" t="s">
         <v>187</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" t="s">
         <v>188</v>
-      </c>
-      <c r="C32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" t="s">
-        <v>189</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G32" t="s">
         <v>29</v>
@@ -3897,7 +3894,7 @@
         <v>60</v>
       </c>
       <c r="Q32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R32" t="s">
         <v>35</v>
@@ -3926,22 +3923,22 @@
     </row>
     <row r="33" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" t="s">
         <v>190</v>
-      </c>
-      <c r="B33" t="s">
-        <v>192</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>191</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
         <v>29</v>
@@ -3974,7 +3971,7 @@
         <v>60</v>
       </c>
       <c r="Q33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R33" t="s">
         <v>35</v>
@@ -4003,22 +4000,22 @@
     </row>
     <row r="34" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" t="s">
         <v>193</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" t="s">
         <v>194</v>
-      </c>
-      <c r="C34" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" t="s">
-        <v>195</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
         <v>29</v>
@@ -4051,7 +4048,7 @@
         <v>60</v>
       </c>
       <c r="Q34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R34" t="s">
         <v>35</v>
@@ -4080,22 +4077,22 @@
     </row>
     <row r="35" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B35" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G35" t="s">
         <v>29</v>
@@ -4157,22 +4154,22 @@
     </row>
     <row r="36" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C36" t="s">
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G36" t="s">
         <v>29</v>
@@ -4234,16 +4231,16 @@
     </row>
     <row r="37" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -4311,22 +4308,22 @@
     </row>
     <row r="38" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" t="s">
         <v>209</v>
       </c>
-      <c r="B38" t="s">
-        <v>210</v>
-      </c>
       <c r="C38" t="s">
+        <v>204</v>
+      </c>
+      <c r="D38" t="s">
         <v>205</v>
-      </c>
-      <c r="D38" t="s">
-        <v>206</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G38" t="s">
         <v>29</v>
@@ -4335,7 +4332,7 @@
         <v>24</v>
       </c>
       <c r="I38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J38" t="s">
         <v>25</v>
@@ -4356,10 +4353,10 @@
         <v>56</v>
       </c>
       <c r="P38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R38" t="s">
         <v>35</v>
@@ -4388,22 +4385,22 @@
     </row>
     <row r="39" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" t="s">
+        <v>213</v>
+      </c>
+      <c r="D39" t="s">
         <v>215</v>
-      </c>
-      <c r="C39" t="s">
-        <v>214</v>
-      </c>
-      <c r="D39" t="s">
-        <v>216</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G39" t="s">
         <v>29</v>
@@ -4412,7 +4409,7 @@
         <v>24</v>
       </c>
       <c r="I39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J39" t="s">
         <v>25</v>
@@ -4433,10 +4430,10 @@
         <v>56</v>
       </c>
       <c r="P39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R39" t="s">
         <v>35</v>
@@ -4465,22 +4462,22 @@
     </row>
     <row r="40" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>217</v>
+      </c>
+      <c r="B40" t="s">
+        <v>220</v>
+      </c>
+      <c r="C40" t="s">
+        <v>216</v>
+      </c>
+      <c r="D40" t="s">
         <v>218</v>
-      </c>
-      <c r="B40" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" t="s">
-        <v>217</v>
-      </c>
-      <c r="D40" t="s">
-        <v>219</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G40" t="s">
         <v>29</v>
@@ -4489,7 +4486,7 @@
         <v>24</v>
       </c>
       <c r="I40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J40" t="s">
         <v>25</v>
@@ -4510,10 +4507,10 @@
         <v>56</v>
       </c>
       <c r="P40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R40" t="s">
         <v>35</v>
@@ -5498,6 +5495,7 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <autoFilter ref="A1:Y40" xr:uid="{DE022BA9-0585-402B-B4A1-87C9075B868E}"/>
   <dataValidations count="1">
     <dataValidation type="decimal" allowBlank="1" sqref="T2:X5001 K2:N5001" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>-9223372036854770000</formula1>
